--- a/Luca/luca_bert_benchmark_results.xlsx
+++ b/Luca/luca_bert_benchmark_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,6 +567,31 @@
           <t>timestamp</t>
         </is>
       </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mean_transcription_time</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>entertainment_mean_transcription_time</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>science_nature_mean_transcription_time</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>ancient_history_mean_transcription_time</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>maths_mean_transcription_time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -663,6 +688,11 @@
           <t>2026-05-14 14:40:46</t>
         </is>
       </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -758,6 +788,677 @@
         <is>
           <t>2026-05-14 16:20:21</t>
         </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>243159dd0f5843ab89038c179f435c6c</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Luca</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BERT baseline</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>nomic-ai/nomic-embed-text-v1.5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.4452150234809288</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.4448849879778348</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2069380760192871</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2066437244415283</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5405943791071574</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.5402674674987793</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.401858401298523</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.4015099287033081</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.6557499885559082</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.6554173946380615</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:50:40</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.584167883946345</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.107781934738159</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.87276836236318</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.520761322975159</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.841046380996704</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>975cd7f0e7e14fe9a575339450961293</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Luca</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BERT baseline</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>nomic-ai/nomic-embed-text-v1.5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2911784052848816</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2908730506896973</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5714170932769775</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5710999965667725</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.183234691619873</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.182997465133667</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1942739486694336</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.1939516067504883</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.2157878875732422</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.2154431343078613</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:13:15</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.780369877815247</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3.208831548690796</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4.384173393249512</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.462116003036499</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.06635856628418</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>67bf68f0d6b94c349d46c9db1351209b</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Luca</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BERT baseline</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>nomic-ai/nomic-embed-text-v1.5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.154545090415261</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1544749520041726</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1504265069961548</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1503596305847168</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1463399410247803</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1462738990783691</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.1483328342437744</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.1482627391815186</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1853888034820557</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.185305118560791</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:31:07</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.578542232513428</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.831495046615601</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.249647951126099</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.770892739295959</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.955474615097046</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>359e5bfbab0a4263a745f61e5e085b29</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Luca</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BERT baseline</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>nomic-ai/nomic-embed-text-v1.5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1744411256578234</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1743675337897407</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1598172187805176</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1597537994384766</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1805174350738525</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.1804242134094238</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1775134801864624</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.1774474382400513</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.1872283220291138</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.1871515512466431</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:39:29</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.0243767897288</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.552304665247599</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.9736558198928833</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.180481553077698</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.127101182937622</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2e5fd8139593471383c26b434b8984af</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Luca</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BERT baseline</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>nomic-ai/nomic-embed-text-v1.5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1678167411259242</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1677419628415789</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.1856296062469482</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1855299472808838</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1517053604125977</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.1516367912292481</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1663495898246765</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.1662859320640564</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.1843101978302002</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.1842349767684937</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:45:35</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.130542959485735</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.900192658106486</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.335881233215332</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.48925906419754</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>3.245290517807007</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>558348de7eaf4372bbc4456fb55926b8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Luca</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BERT baseline</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>nomic-ai/nomic-embed-text-v1.5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2072047970511696</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2071279829198664</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2061583201090495</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2060738404591878</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1857990026473999</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.1857191324234009</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.1876724561055501</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.1876034736633301</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.2420541445414225</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.2419792016347249</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:54:24</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>4.122640349648216</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>4.126583258310954</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.827072024345398</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3.405505657196045</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5.032877683639526</v>
       </c>
     </row>
   </sheetData>

--- a/Luca/luca_bert_benchmark_results.xlsx
+++ b/Luca/luca_bert_benchmark_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1461,6 +1461,117 @@
         <v>5.032877683639526</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>a0134a8b2e694bc0823143af5fe5cef4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Luca</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BERT baseline</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>nomic-ai/nomic-embed-text-v1.5</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3845967905861991</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3841581004006522</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5916048288345337</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5910089015960693</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2890947659810384</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.2887144883473714</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.3072278499603271</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3068766593933105</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.3344557285308838</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.334068775177002</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:10:47</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.848027638026646</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.958618760108948</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4.071464856465657</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3.941786766052246</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2.862774610519409</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
